--- a/extenbooks/XS005_extenbook.xlsx
+++ b/extenbooks/XS005_extenbook.xlsx
@@ -764,7 +764,7 @@
         <v>1930</v>
       </c>
       <c r="B9" t="n">
-        <v>98.69751034729497</v>
+        <v>98.69751034729495</v>
       </c>
       <c r="C9" t="n">
         <v>98.5</v>
@@ -890,13 +890,13 @@
         <v>1939</v>
       </c>
       <c r="B18" t="n">
-        <v>94.38998174480436</v>
+        <v>94.38998174480437</v>
       </c>
       <c r="C18" t="n">
         <v>94.40000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9998938744153004</v>
+        <v>0.9998938744153005</v>
       </c>
     </row>
     <row r="19">
@@ -952,7 +952,7 @@
         <v>119.3</v>
       </c>
       <c r="D22" t="n">
-        <v>1.000413401093564</v>
+        <v>1.000413401093563</v>
       </c>
     </row>
     <row r="23">
@@ -1008,7 +1008,7 @@
         <v>190.1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.994430096174702</v>
+        <v>0.9944300961747021</v>
       </c>
     </row>
     <row r="27">
@@ -1022,7 +1022,7 @@
         <v>208.1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9941071901382824</v>
+        <v>0.9941071901382825</v>
       </c>
     </row>
     <row r="28">
@@ -1064,7 +1064,7 @@
         <v>258.5</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9938759259463968</v>
+        <v>0.9938759259463967</v>
       </c>
     </row>
     <row r="31">
@@ -1078,7 +1078,7 @@
         <v>273.5</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9938297772931332</v>
+        <v>0.9938297772931333</v>
       </c>
     </row>
     <row r="32">
@@ -1092,7 +1092,7 @@
         <v>287</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9941143551806564</v>
+        <v>0.9941143551806563</v>
       </c>
     </row>
     <row r="33">
@@ -1120,7 +1120,7 @@
         <v>325</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9936543011532272</v>
+        <v>0.9936543011532273</v>
       </c>
     </row>
     <row r="35">
@@ -1134,7 +1134,7 @@
         <v>360.7</v>
       </c>
       <c r="D35" t="n">
-        <v>0.993131636908824</v>
+        <v>0.9931316369088241</v>
       </c>
     </row>
     <row r="36">
@@ -1148,7 +1148,7 @@
         <v>386.9</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9932381971000072</v>
+        <v>0.9932381971000073</v>
       </c>
     </row>
     <row r="37">
@@ -1190,7 +1190,7 @@
         <v>419.9</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9942540346388404</v>
+        <v>0.9942540346388405</v>
       </c>
     </row>
     <row r="40">
@@ -1204,7 +1204,7 @@
         <v>430.3</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9945841615285804</v>
+        <v>0.9945841615285803</v>
       </c>
     </row>
     <row r="41">
@@ -1218,7 +1218,7 @@
         <v>444.2</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9948606966854652</v>
+        <v>0.9948606966854651</v>
       </c>
     </row>
     <row r="42">
@@ -1232,7 +1232,7 @@
         <v>458.3</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9959791082458188</v>
+        <v>0.9959791082458187</v>
       </c>
     </row>
     <row r="43">
@@ -1260,7 +1260,7 @@
         <v>517.4</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9971174548124044</v>
+        <v>0.9971174548124043</v>
       </c>
     </row>
     <row r="45">
@@ -1288,7 +1288,7 @@
         <v>610.8</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9957940612804324</v>
+        <v>0.9957940612804325</v>
       </c>
     </row>
     <row r="47">
@@ -1302,7 +1302,7 @@
         <v>672.6</v>
       </c>
       <c r="D47" t="n">
-        <v>0.994952425421004</v>
+        <v>0.9949524254210041</v>
       </c>
     </row>
     <row r="48">
@@ -1372,7 +1372,7 @@
         <v>1097.4</v>
       </c>
       <c r="D52" t="n">
-        <v>0.992971914890468</v>
+        <v>0.9929719148904681</v>
       </c>
     </row>
     <row r="53">
@@ -1400,7 +1400,7 @@
         <v>1495.4</v>
       </c>
       <c r="D54" t="n">
-        <v>0.9900390553415784</v>
+        <v>0.9900390553415785</v>
       </c>
     </row>
     <row r="55">
@@ -1470,7 +1470,7 @@
         <v>2761.2</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9876538794822</v>
+        <v>0.9876538794822001</v>
       </c>
     </row>
     <row r="60">
@@ -1484,7 +1484,7 @@
         <v>3125.3</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9873066826276904</v>
+        <v>0.9873066826276905</v>
       </c>
     </row>
     <row r="61">
@@ -1520,7 +1520,7 @@
         <v>1984</v>
       </c>
       <c r="B63" t="n">
-        <v>3582.76869090992</v>
+        <v>3582.768690909919</v>
       </c>
       <c r="C63" t="n">
         <v>3618.4</v>
@@ -1540,7 +1540,7 @@
         <v>3819.3</v>
       </c>
       <c r="D64" t="n">
-        <v>0.9908738638786776</v>
+        <v>0.9908738638786777</v>
       </c>
     </row>
     <row r="65">
@@ -1568,7 +1568,7 @@
         <v>4197.6</v>
       </c>
       <c r="D66" t="n">
-        <v>0.9919864157321016</v>
+        <v>0.9919864157321017</v>
       </c>
     </row>
     <row r="67">
@@ -1680,7 +1680,7 @@
         <v>6154.2</v>
       </c>
       <c r="D74" t="n">
-        <v>0.9971400191097876</v>
+        <v>0.9971400191097877</v>
       </c>
     </row>
     <row r="75">
@@ -1694,7 +1694,7 @@
         <v>6469.9</v>
       </c>
       <c r="D75" t="n">
-        <v>0.9971715975659508</v>
+        <v>0.9971715975659509</v>
       </c>
     </row>
     <row r="76">
@@ -1722,7 +1722,7 @@
         <v>7217.6</v>
       </c>
       <c r="D77" t="n">
-        <v>0.9971937468515748</v>
+        <v>0.9971937468515747</v>
       </c>
     </row>
     <row r="78">
@@ -1750,7 +1750,7 @@
         <v>8175.4</v>
       </c>
       <c r="D79" t="n">
-        <v>0.9974590993000324</v>
+        <v>0.9974590993000325</v>
       </c>
     </row>
     <row r="80">
@@ -1792,7 +1792,7 @@
         <v>9185.799999999999</v>
       </c>
       <c r="D82" t="n">
-        <v>0.9992205147868012</v>
+        <v>0.9992205147868013</v>
       </c>
     </row>
     <row r="83">
@@ -1848,7 +1848,7 @@
         <v>12317.8</v>
       </c>
       <c r="D86" t="n">
-        <v>0.9999703914157824</v>
+        <v>0.9999703914157825</v>
       </c>
     </row>
     <row r="87">
@@ -1890,7 +1890,7 @@
         <v>12994.6</v>
       </c>
       <c r="D89" t="n">
-        <v>1.00012809091</v>
+        <v>1.000128090910001</v>
       </c>
     </row>
     <row r="90">
@@ -1969,14 +1969,14 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B97" t="n">
-        <v>98.09999999999999</v>
+        <v>101.0183856502242</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -1992,14 +1992,14 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>102.4992588297177</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2015,10 +2015,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="B99" t="n">
-        <v>101.0183856502242</v>
+        <v>104.7900247718437</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -2038,14 +2038,14 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1926</v>
+        <v>1929</v>
       </c>
       <c r="B100" t="n">
-        <v>101</v>
+        <v>103.708792215535</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2061,14 +2061,14 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="B101" t="n">
-        <v>1.000182036140834</v>
+        <v>98.69751034729495</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2084,10 +2084,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1927</v>
+        <v>1931</v>
       </c>
       <c r="B102" t="n">
-        <v>102.4992588297177</v>
+        <v>88.54049954523617</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -2107,14 +2107,14 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1927</v>
+        <v>1932</v>
       </c>
       <c r="B103" t="n">
-        <v>102.4</v>
+        <v>82.51476423499568</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2130,14 +2130,14 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
       <c r="B104" t="n">
-        <v>1.000969324508962</v>
+        <v>83.37798310417058</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2153,10 +2153,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1928</v>
+        <v>1934</v>
       </c>
       <c r="B105" t="n">
-        <v>104.7900247718437</v>
+        <v>84.32944287028377</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2176,14 +2176,14 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1928</v>
+        <v>1935</v>
       </c>
       <c r="B106" t="n">
-        <v>104.7</v>
+        <v>83.88818092520748</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2199,14 +2199,14 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1928</v>
+        <v>1936</v>
       </c>
       <c r="B107" t="n">
-        <v>1.000859835452184</v>
+        <v>92.108108568649</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2222,10 +2222,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1929</v>
+        <v>1937</v>
       </c>
       <c r="B108" t="n">
-        <v>103.708792215535</v>
+        <v>95.30173765222506</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2245,14 +2245,14 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1929</v>
+        <v>1938</v>
       </c>
       <c r="B109" t="n">
-        <v>103.6</v>
+        <v>93.98677847785156</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2268,14 +2268,14 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1929</v>
+        <v>1939</v>
       </c>
       <c r="B110" t="n">
-        <v>1.00105011791057</v>
+        <v>94.38998174480437</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2291,10 +2291,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1930</v>
+        <v>1940</v>
       </c>
       <c r="B111" t="n">
-        <v>98.69751034729497</v>
+        <v>100.1271191385587</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2314,14 +2314,14 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1930</v>
+        <v>1941</v>
       </c>
       <c r="B112" t="n">
-        <v>98.5</v>
+        <v>112.0964129892014</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2337,14 +2337,14 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1930</v>
+        <v>1942</v>
       </c>
       <c r="B113" t="n">
-        <v>1.002005181190812</v>
+        <v>118.8577738150732</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -2360,10 +2360,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1931</v>
+        <v>1943</v>
       </c>
       <c r="B114" t="n">
-        <v>88.54049954523617</v>
+        <v>119.3493187504621</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2383,14 +2383,14 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1931</v>
+        <v>1944</v>
       </c>
       <c r="B115" t="n">
-        <v>88.40000000000001</v>
+        <v>120.2215232131932</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -2406,14 +2406,14 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1931</v>
+        <v>1945</v>
       </c>
       <c r="B116" t="n">
-        <v>1.00158936137145</v>
+        <v>131.1996878155243</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -2429,10 +2429,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1932</v>
+        <v>1946</v>
       </c>
       <c r="B117" t="n">
-        <v>82.51476423499568</v>
+        <v>158.8067935361755</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -2452,14 +2452,14 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1932</v>
+        <v>1947</v>
       </c>
       <c r="B118" t="n">
-        <v>82.40000000000001</v>
+        <v>189.0411612828109</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -2475,14 +2475,14 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1932</v>
+        <v>1948</v>
       </c>
       <c r="B119" t="n">
-        <v>1.001392769842181</v>
+        <v>206.8737062677766</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -2498,10 +2498,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1933</v>
+        <v>1949</v>
       </c>
       <c r="B120" t="n">
-        <v>83.37798310417058</v>
+        <v>211.0739821250903</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -2521,14 +2521,14 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1933</v>
+        <v>1950</v>
       </c>
       <c r="B121" t="n">
-        <v>83.2</v>
+        <v>236.5210037775323</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2544,14 +2544,14 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1933</v>
+        <v>1951</v>
       </c>
       <c r="B122" t="n">
-        <v>1.00213922000205</v>
+        <v>256.9169268571436</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -2567,10 +2567,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1934</v>
+        <v>1952</v>
       </c>
       <c r="B123" t="n">
-        <v>84.32944287028377</v>
+        <v>271.8124440896719</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -2590,14 +2590,14 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1934</v>
+        <v>1953</v>
       </c>
       <c r="B124" t="n">
-        <v>84.2</v>
+        <v>285.3108199368484</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -2613,14 +2613,14 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1934</v>
+        <v>1954</v>
       </c>
       <c r="B125" t="n">
-        <v>1.001537326250401</v>
+        <v>293.7023418634677</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -2636,10 +2636,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1935</v>
+        <v>1955</v>
       </c>
       <c r="B126" t="n">
-        <v>83.88818092520748</v>
+        <v>322.9376478747989</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -2659,14 +2659,14 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1935</v>
+        <v>1956</v>
       </c>
       <c r="B127" t="n">
-        <v>83.7</v>
+        <v>358.2225814330129</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -2682,14 +2682,14 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1935</v>
+        <v>1957</v>
       </c>
       <c r="B128" t="n">
-        <v>1.002248278676314</v>
+        <v>384.2838584579928</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -2705,10 +2705,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1936</v>
+        <v>1958</v>
       </c>
       <c r="B129" t="n">
-        <v>92.108108568649</v>
+        <v>391.8943218769265</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -2728,14 +2728,14 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1936</v>
+        <v>1959</v>
       </c>
       <c r="B130" t="n">
-        <v>92</v>
+        <v>409.1409002831265</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -2751,14 +2751,14 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1936</v>
+        <v>1960</v>
       </c>
       <c r="B131" t="n">
-        <v>1.001175093137489</v>
+        <v>417.4872691448491</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -2774,10 +2774,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1937</v>
+        <v>1961</v>
       </c>
       <c r="B132" t="n">
-        <v>95.30173765222506</v>
+        <v>427.9695647057481</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -2797,14 +2797,14 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1937</v>
+        <v>1962</v>
       </c>
       <c r="B133" t="n">
-        <v>95.2</v>
+        <v>441.9171214676836</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -2820,14 +2820,14 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1937</v>
+        <v>1963</v>
       </c>
       <c r="B134" t="n">
-        <v>1.00106867281749</v>
+        <v>456.4572253090587</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -2843,10 +2843,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1938</v>
+        <v>1964</v>
       </c>
       <c r="B135" t="n">
-        <v>93.98677847785156</v>
+        <v>482.3239550040442</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -2866,14 +2866,14 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1938</v>
+        <v>1965</v>
       </c>
       <c r="B136" t="n">
-        <v>93.90000000000001</v>
+        <v>515.908571119938</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -2889,14 +2889,14 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1938</v>
+        <v>1966</v>
       </c>
       <c r="B137" t="n">
-        <v>1.000924158443574</v>
+        <v>561.3369755375326</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -2912,10 +2912,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1939</v>
+        <v>1967</v>
       </c>
       <c r="B138" t="n">
-        <v>94.38998174480436</v>
+        <v>608.2310126300881</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -2935,14 +2935,14 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1939</v>
+        <v>1968</v>
       </c>
       <c r="B139" t="n">
-        <v>94.40000000000001</v>
+        <v>669.2050013381674</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -2958,14 +2958,14 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1939</v>
+        <v>1969</v>
       </c>
       <c r="B140" t="n">
-        <v>0.9998938744153004</v>
+        <v>736.7840182637449</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -2981,10 +2981,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1940</v>
+        <v>1970</v>
       </c>
       <c r="B141" t="n">
-        <v>100.1271191385587</v>
+        <v>810.5926363043061</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -3004,14 +3004,14 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1940</v>
+        <v>1971</v>
       </c>
       <c r="B142" t="n">
-        <v>100.1</v>
+        <v>889.3523429438201</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3027,14 +3027,14 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1940</v>
+        <v>1972</v>
       </c>
       <c r="B143" t="n">
-        <v>1.000270920465122</v>
+        <v>966.1726056334739</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3050,10 +3050,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1941</v>
+        <v>1973</v>
       </c>
       <c r="B144" t="n">
-        <v>112.0964129892014</v>
+        <v>1089.6873794008</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -3073,14 +3073,14 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1941</v>
+        <v>1974</v>
       </c>
       <c r="B145" t="n">
-        <v>112.1</v>
+        <v>1332.978935746061</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3096,14 +3096,14 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1941</v>
+        <v>1975</v>
       </c>
       <c r="B146" t="n">
-        <v>0.999968001687791</v>
+        <v>1480.504403357797</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1942</v>
+        <v>1976</v>
       </c>
       <c r="B147" t="n">
-        <v>118.8577738150732</v>
+        <v>1627.395099145966</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -3142,14 +3142,14 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1942</v>
+        <v>1977</v>
       </c>
       <c r="B148" t="n">
-        <v>118.9</v>
+        <v>1811.615021117053</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3165,14 +3165,14 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1942</v>
+        <v>1978</v>
       </c>
       <c r="B149" t="n">
-        <v>0.999644859672609</v>
+        <v>2058.990768098445</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3188,10 +3188,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1943</v>
+        <v>1979</v>
       </c>
       <c r="B150" t="n">
-        <v>119.3493187504621</v>
+        <v>2372.315432853952</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -3211,14 +3211,14 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1943</v>
+        <v>1980</v>
       </c>
       <c r="B151" t="n">
-        <v>119.3</v>
+        <v>2727.109892026251</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3234,14 +3234,14 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1943</v>
+        <v>1981</v>
       </c>
       <c r="B152" t="n">
-        <v>1.000413401093564</v>
+        <v>3085.629575216321</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3257,10 +3257,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1944</v>
+        <v>1982</v>
       </c>
       <c r="B153" t="n">
-        <v>120.2215232131932</v>
+        <v>3280.5613982554</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -3280,14 +3280,14 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1944</v>
+        <v>1983</v>
       </c>
       <c r="B154" t="n">
-        <v>120.2</v>
+        <v>3379.52703688241</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3303,14 +3303,14 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1944</v>
+        <v>1984</v>
       </c>
       <c r="B155" t="n">
-        <v>1.00017906167382</v>
+        <v>3582.768690909919</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3326,10 +3326,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>1945</v>
+        <v>1985</v>
       </c>
       <c r="B156" t="n">
-        <v>131.1996878155243</v>
+        <v>3784.444548311834</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -3349,14 +3349,14 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1945</v>
+        <v>1986</v>
       </c>
       <c r="B157" t="n">
-        <v>131.2</v>
+        <v>3955.988767242127</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -3372,14 +3372,14 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1945</v>
+        <v>1987</v>
       </c>
       <c r="B158" t="n">
-        <v>0.9999976205451548</v>
+        <v>4163.96217867707</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3395,10 +3395,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1946</v>
+        <v>1988</v>
       </c>
       <c r="B159" t="n">
-        <v>158.8067935361755</v>
+        <v>4428.610001509143</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -3418,14 +3418,14 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1946</v>
+        <v>1989</v>
       </c>
       <c r="B160" t="n">
-        <v>159.4</v>
+        <v>4696.527407332671</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -3441,14 +3441,14 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1946</v>
+        <v>1990</v>
       </c>
       <c r="B161" t="n">
-        <v>0.9962785039910634</v>
+        <v>4961.119421061194</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3464,10 +3464,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1947</v>
+        <v>1991</v>
       </c>
       <c r="B162" t="n">
-        <v>189.0411612828109</v>
+        <v>5075.528851661904</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -3487,14 +3487,14 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1947</v>
+        <v>1992</v>
       </c>
       <c r="B163" t="n">
-        <v>190.1</v>
+        <v>5250.82411907481</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -3510,14 +3510,14 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1947</v>
+        <v>1993</v>
       </c>
       <c r="B164" t="n">
-        <v>0.994430096174702</v>
+        <v>5500.592856221755</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -3533,10 +3533,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>1948</v>
+        <v>1994</v>
       </c>
       <c r="B165" t="n">
-        <v>206.8737062677766</v>
+        <v>5805.960443253049</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -3556,14 +3556,14 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>1948</v>
+        <v>1995</v>
       </c>
       <c r="B166" t="n">
-        <v>208.1</v>
+        <v>6136.599105605455</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -3579,14 +3579,14 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>1948</v>
+        <v>1996</v>
       </c>
       <c r="B167" t="n">
-        <v>0.9941071901382824</v>
+        <v>6451.600519091945</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -3602,10 +3602,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1949</v>
+        <v>1997</v>
       </c>
       <c r="B168" t="n">
-        <v>211.0739821250903</v>
+        <v>6812.173917136629</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -3625,14 +3625,14 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1949</v>
+        <v>1998</v>
       </c>
       <c r="B169" t="n">
-        <v>212.2</v>
+        <v>7197.345587275926</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -3648,14 +3648,14 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1949</v>
+        <v>1999</v>
       </c>
       <c r="B170" t="n">
-        <v>0.9946936009664952</v>
+        <v>7621.627746178</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -3671,10 +3671,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1950</v>
+        <v>2000</v>
       </c>
       <c r="B171" t="n">
-        <v>236.5210037775323</v>
+        <v>8154.627120417485</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -3694,14 +3694,14 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1950</v>
+        <v>2001</v>
       </c>
       <c r="B172" t="n">
-        <v>238.1</v>
+        <v>8588.950335181662</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -3717,14 +3717,14 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1950</v>
+        <v>2002</v>
       </c>
       <c r="B173" t="n">
-        <v>0.9933683484986656</v>
+        <v>8900.840268850468</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -3740,10 +3740,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1951</v>
+        <v>2003</v>
       </c>
       <c r="B174" t="n">
-        <v>256.9169268571436</v>
+        <v>9178.639804728598</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -3763,14 +3763,14 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1951</v>
+        <v>2004</v>
       </c>
       <c r="B175" t="n">
-        <v>258.5</v>
+        <v>9904.847948333394</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -3786,14 +3786,14 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>1951</v>
+        <v>2005</v>
       </c>
       <c r="B176" t="n">
-        <v>0.9938759259463968</v>
+        <v>10780.81498817506</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -3809,10 +3809,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1952</v>
+        <v>2006</v>
       </c>
       <c r="B177" t="n">
-        <v>271.8124440896719</v>
+        <v>11684.02682902413</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -3832,14 +3832,14 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>1952</v>
+        <v>2007</v>
       </c>
       <c r="B178" t="n">
-        <v>273.5</v>
+        <v>12317.43528738132</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -3855,14 +3855,14 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>1952</v>
+        <v>2008</v>
       </c>
       <c r="B179" t="n">
-        <v>0.9938297772931332</v>
+        <v>13141.3387796931</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -3878,10 +3878,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>1953</v>
+        <v>2009</v>
       </c>
       <c r="B180" t="n">
-        <v>285.3108199368484</v>
+        <v>12704.12906671262</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -3901,14 +3901,14 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>1953</v>
+        <v>2010</v>
       </c>
       <c r="B181" t="n">
-        <v>287</v>
+        <v>12996.26449013909</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -3924,14 +3924,14 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>1953</v>
+        <v>2011</v>
       </c>
       <c r="B182" t="n">
-        <v>0.9941143551806564</v>
+        <v>13531.21957541143</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-A</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -3947,14 +3947,14 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1954</v>
+        <v>1925</v>
       </c>
       <c r="B183" t="n">
-        <v>293.7023418634677</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -3970,10 +3970,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>1954</v>
+        <v>1926</v>
       </c>
       <c r="B184" t="n">
-        <v>295.3</v>
+        <v>101</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -3993,14 +3993,14 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>1954</v>
+        <v>1927</v>
       </c>
       <c r="B185" t="n">
-        <v>0.9945897116947772</v>
+        <v>102.4</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4016,14 +4016,14 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>1955</v>
+        <v>1928</v>
       </c>
       <c r="B186" t="n">
-        <v>322.9376478747989</v>
+        <v>104.7</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4039,10 +4039,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1955</v>
+        <v>1929</v>
       </c>
       <c r="B187" t="n">
-        <v>325</v>
+        <v>103.6</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -4062,14 +4062,14 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1955</v>
+        <v>1930</v>
       </c>
       <c r="B188" t="n">
-        <v>0.9936543011532272</v>
+        <v>98.5</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4085,14 +4085,14 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>1956</v>
+        <v>1931</v>
       </c>
       <c r="B189" t="n">
-        <v>358.2225814330129</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4108,10 +4108,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>1956</v>
+        <v>1932</v>
       </c>
       <c r="B190" t="n">
-        <v>360.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -4131,14 +4131,14 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1956</v>
+        <v>1933</v>
       </c>
       <c r="B191" t="n">
-        <v>0.993131636908824</v>
+        <v>83.2</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4154,14 +4154,14 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>1957</v>
+        <v>1934</v>
       </c>
       <c r="B192" t="n">
-        <v>384.2838584579928</v>
+        <v>84.2</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4177,10 +4177,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>1957</v>
+        <v>1935</v>
       </c>
       <c r="B193" t="n">
-        <v>386.9</v>
+        <v>83.7</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -4200,14 +4200,14 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>1957</v>
+        <v>1936</v>
       </c>
       <c r="B194" t="n">
-        <v>0.9932381971000072</v>
+        <v>92</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4223,14 +4223,14 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>1958</v>
+        <v>1937</v>
       </c>
       <c r="B195" t="n">
-        <v>391.8943218769265</v>
+        <v>95.2</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4246,10 +4246,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>1958</v>
+        <v>1938</v>
       </c>
       <c r="B196" t="n">
-        <v>394.4</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -4269,14 +4269,14 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>1958</v>
+        <v>1939</v>
       </c>
       <c r="B197" t="n">
-        <v>0.9936468607427142</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4292,14 +4292,14 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>1959</v>
+        <v>1940</v>
       </c>
       <c r="B198" t="n">
-        <v>409.1409002831265</v>
+        <v>100.1</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4315,10 +4315,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>1959</v>
+        <v>1941</v>
       </c>
       <c r="B199" t="n">
-        <v>411.6</v>
+        <v>112.1</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -4338,14 +4338,14 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>1959</v>
+        <v>1942</v>
       </c>
       <c r="B200" t="n">
-        <v>0.9940255108919498</v>
+        <v>118.9</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -4361,14 +4361,14 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>1960</v>
+        <v>1943</v>
       </c>
       <c r="B201" t="n">
-        <v>417.4872691448491</v>
+        <v>119.3</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -4384,10 +4384,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>1960</v>
+        <v>1944</v>
       </c>
       <c r="B202" t="n">
-        <v>419.9</v>
+        <v>120.2</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -4407,14 +4407,14 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>1960</v>
+        <v>1945</v>
       </c>
       <c r="B203" t="n">
-        <v>0.9942540346388404</v>
+        <v>131.2</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -4430,14 +4430,14 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>1961</v>
+        <v>1946</v>
       </c>
       <c r="B204" t="n">
-        <v>427.9695647057481</v>
+        <v>159.4</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -4453,10 +4453,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>1961</v>
+        <v>1947</v>
       </c>
       <c r="B205" t="n">
-        <v>430.3</v>
+        <v>190.1</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -4476,14 +4476,14 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>1961</v>
+        <v>1948</v>
       </c>
       <c r="B206" t="n">
-        <v>0.9945841615285804</v>
+        <v>208.1</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4499,14 +4499,14 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1962</v>
+        <v>1949</v>
       </c>
       <c r="B207" t="n">
-        <v>441.9171214676836</v>
+        <v>212.2</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4522,10 +4522,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1962</v>
+        <v>1950</v>
       </c>
       <c r="B208" t="n">
-        <v>444.2</v>
+        <v>238.1</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -4545,14 +4545,14 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>1962</v>
+        <v>1951</v>
       </c>
       <c r="B209" t="n">
-        <v>0.9948606966854652</v>
+        <v>258.5</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -4568,14 +4568,14 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>1963</v>
+        <v>1952</v>
       </c>
       <c r="B210" t="n">
-        <v>456.4572253090587</v>
+        <v>273.5</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -4591,10 +4591,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1963</v>
+        <v>1953</v>
       </c>
       <c r="B211" t="n">
-        <v>458.3</v>
+        <v>287</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -4614,14 +4614,14 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>1963</v>
+        <v>1954</v>
       </c>
       <c r="B212" t="n">
-        <v>0.9959791082458188</v>
+        <v>295.3</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -4637,14 +4637,14 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>1964</v>
+        <v>1955</v>
       </c>
       <c r="B213" t="n">
-        <v>482.3239550040442</v>
+        <v>325</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -4660,10 +4660,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>1964</v>
+        <v>1956</v>
       </c>
       <c r="B214" t="n">
-        <v>483.9</v>
+        <v>360.7</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -4683,14 +4683,14 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1964</v>
+        <v>1957</v>
       </c>
       <c r="B215" t="n">
-        <v>0.9967430357595458</v>
+        <v>386.9</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -4706,14 +4706,14 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>1965</v>
+        <v>1958</v>
       </c>
       <c r="B216" t="n">
-        <v>515.908571119938</v>
+        <v>394.4</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -4729,10 +4729,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>1965</v>
+        <v>1959</v>
       </c>
       <c r="B217" t="n">
-        <v>517.4</v>
+        <v>411.6</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -4752,14 +4752,14 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1965</v>
+        <v>1960</v>
       </c>
       <c r="B218" t="n">
-        <v>0.9971174548124044</v>
+        <v>419.9</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -4775,14 +4775,14 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>1966</v>
+        <v>1961</v>
       </c>
       <c r="B219" t="n">
-        <v>561.3369755375326</v>
+        <v>430.3</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -4798,10 +4798,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1966</v>
+        <v>1962</v>
       </c>
       <c r="B220" t="n">
-        <v>563.4</v>
+        <v>444.2</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -4821,14 +4821,14 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="B221" t="n">
-        <v>0.9963382597400294</v>
+        <v>458.3</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -4844,14 +4844,14 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="B222" t="n">
-        <v>608.2310126300881</v>
+        <v>483.9</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -4867,10 +4867,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="B223" t="n">
-        <v>610.8</v>
+        <v>517.4</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -4890,14 +4890,14 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B224" t="n">
-        <v>0.9957940612804324</v>
+        <v>563.4</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -4913,14 +4913,14 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B225" t="n">
-        <v>669.2050013381674</v>
+        <v>610.8</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -4959,14 +4959,14 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="B227" t="n">
-        <v>0.994952425421004</v>
+        <v>741.1</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -4982,14 +4982,14 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B228" t="n">
-        <v>736.7840182637449</v>
+        <v>815.7</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -5005,10 +5005,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="B229" t="n">
-        <v>741.1</v>
+        <v>895.2</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -5028,14 +5028,14 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="B230" t="n">
-        <v>0.9941762491752056</v>
+        <v>972.2</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -5051,14 +5051,14 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="B231" t="n">
-        <v>810.5926363043061</v>
+        <v>1097.4</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -5074,10 +5074,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>1970</v>
+        <v>1974</v>
       </c>
       <c r="B232" t="n">
-        <v>815.7</v>
+        <v>1346.4</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -5097,14 +5097,14 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1970</v>
+        <v>1975</v>
       </c>
       <c r="B233" t="n">
-        <v>0.993738673904997</v>
+        <v>1495.4</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -5120,14 +5120,14 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>1971</v>
+        <v>1976</v>
       </c>
       <c r="B234" t="n">
-        <v>889.3523429438201</v>
+        <v>1643.8</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -5143,10 +5143,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1971</v>
+        <v>1977</v>
       </c>
       <c r="B235" t="n">
-        <v>895.2</v>
+        <v>1829.9</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -5166,14 +5166,14 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>1971</v>
+        <v>1978</v>
       </c>
       <c r="B236" t="n">
-        <v>0.9934677646825514</v>
+        <v>2081.5</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -5189,14 +5189,14 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>1972</v>
+        <v>1979</v>
       </c>
       <c r="B237" t="n">
-        <v>966.1726056334739</v>
+        <v>2399.7</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -5212,10 +5212,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>1972</v>
+        <v>1980</v>
       </c>
       <c r="B238" t="n">
-        <v>972.2</v>
+        <v>2761.2</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -5235,14 +5235,14 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1972</v>
+        <v>1981</v>
       </c>
       <c r="B239" t="n">
-        <v>0.9938002526573482</v>
+        <v>3125.3</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -5258,14 +5258,14 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1973</v>
+        <v>1982</v>
       </c>
       <c r="B240" t="n">
-        <v>1089.6873794008</v>
+        <v>3318.6</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -5281,10 +5281,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1973</v>
+        <v>1983</v>
       </c>
       <c r="B241" t="n">
-        <v>1097.4</v>
+        <v>3415.3</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -5304,14 +5304,14 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1973</v>
+        <v>1984</v>
       </c>
       <c r="B242" t="n">
-        <v>0.992971914890468</v>
+        <v>3618.4</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -5327,14 +5327,14 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>1974</v>
+        <v>1985</v>
       </c>
       <c r="B243" t="n">
-        <v>1332.978935746061</v>
+        <v>3819.3</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -5350,10 +5350,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>1974</v>
+        <v>1986</v>
       </c>
       <c r="B244" t="n">
-        <v>1346.4</v>
+        <v>3989.7</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -5373,14 +5373,14 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>1974</v>
+        <v>1987</v>
       </c>
       <c r="B245" t="n">
-        <v>0.9900318892944598</v>
+        <v>4197.6</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -5396,14 +5396,14 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>1975</v>
+        <v>1988</v>
       </c>
       <c r="B246" t="n">
-        <v>1480.504403357797</v>
+        <v>4462.9</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -5419,10 +5419,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>1975</v>
+        <v>1989</v>
       </c>
       <c r="B247" t="n">
-        <v>1495.4</v>
+        <v>4728.2</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -5442,14 +5442,14 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>1975</v>
+        <v>1990</v>
       </c>
       <c r="B248" t="n">
-        <v>0.9900390553415784</v>
+        <v>4993.1</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -5465,14 +5465,14 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1976</v>
+        <v>1991</v>
       </c>
       <c r="B249" t="n">
-        <v>1627.395099145966</v>
+        <v>5105.1</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -5488,10 +5488,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1976</v>
+        <v>1992</v>
       </c>
       <c r="B250" t="n">
-        <v>1643.8</v>
+        <v>5275.6</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -5511,14 +5511,14 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>1976</v>
+        <v>1993</v>
       </c>
       <c r="B251" t="n">
-        <v>0.9900201357500704</v>
+        <v>5523.9</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -5534,14 +5534,14 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>1977</v>
+        <v>1994</v>
       </c>
       <c r="B252" t="n">
-        <v>1811.615021117053</v>
+        <v>5823.9</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -5557,10 +5557,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>1977</v>
+        <v>1995</v>
       </c>
       <c r="B253" t="n">
-        <v>1829.9</v>
+        <v>6154.2</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -5580,14 +5580,14 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>1977</v>
+        <v>1996</v>
       </c>
       <c r="B254" t="n">
-        <v>0.9900076622312982</v>
+        <v>6469.9</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -5603,14 +5603,14 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>1978</v>
+        <v>1997</v>
       </c>
       <c r="B255" t="n">
-        <v>2058.990768098445</v>
+        <v>6830.5</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -5626,10 +5626,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>1978</v>
+        <v>1998</v>
       </c>
       <c r="B256" t="n">
-        <v>2081.5</v>
+        <v>7217.6</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -5649,14 +5649,14 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>1978</v>
+        <v>1999</v>
       </c>
       <c r="B257" t="n">
-        <v>0.9891860524133774</v>
+        <v>7641.6</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -5672,14 +5672,14 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>1979</v>
+        <v>2000</v>
       </c>
       <c r="B258" t="n">
-        <v>2372.315432853952</v>
+        <v>8175.4</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -5695,10 +5695,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>1979</v>
+        <v>2001</v>
       </c>
       <c r="B259" t="n">
-        <v>2399.7</v>
+        <v>8595.6</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -5718,14 +5718,14 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1979</v>
+        <v>2002</v>
       </c>
       <c r="B260" t="n">
-        <v>0.9885883372313006</v>
+        <v>8907.700000000001</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -5741,14 +5741,14 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="B261" t="n">
-        <v>2727.109892026251</v>
+        <v>9185.799999999999</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -5764,10 +5764,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1980</v>
+        <v>2004</v>
       </c>
       <c r="B262" t="n">
-        <v>2761.2</v>
+        <v>9909.5</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -5787,14 +5787,14 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1980</v>
+        <v>2005</v>
       </c>
       <c r="B263" t="n">
-        <v>0.9876538794822</v>
+        <v>10768.3</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -5810,14 +5810,14 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>1981</v>
+        <v>2006</v>
       </c>
       <c r="B264" t="n">
-        <v>3085.629575216321</v>
+        <v>11679.9</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -5833,10 +5833,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>1981</v>
+        <v>2007</v>
       </c>
       <c r="B265" t="n">
-        <v>3125.3</v>
+        <v>12317.8</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -5856,14 +5856,14 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1981</v>
+        <v>2008</v>
       </c>
       <c r="B266" t="n">
-        <v>0.9873066826276904</v>
+        <v>13138</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -5879,14 +5879,14 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1982</v>
+        <v>2009</v>
       </c>
       <c r="B267" t="n">
-        <v>3280.5613982554</v>
+        <v>12701.7</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -5902,10 +5902,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1982</v>
+        <v>2010</v>
       </c>
       <c r="B268" t="n">
-        <v>3318.6</v>
+        <v>12994.6</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -5925,14 +5925,14 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>1982</v>
+        <v>2011</v>
       </c>
       <c r="B269" t="n">
-        <v>0.9885377563597302</v>
+        <v>13530.8</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>XS005-C</t>
+          <t>XS005-B</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -5948,14 +5948,14 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>1983</v>
+        <v>1925</v>
       </c>
       <c r="B270" t="n">
-        <v>3379.52703688241</v>
+        <v>1</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -5965,20 +5965,20 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1983</v>
+        <v>1926</v>
       </c>
       <c r="B271" t="n">
-        <v>3415.3</v>
+        <v>1.000182036140834</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -5988,16 +5988,16 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1983</v>
+        <v>1927</v>
       </c>
       <c r="B272" t="n">
-        <v>0.9895256747232776</v>
+        <v>1.000969324508962</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -6011,20 +6011,20 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1984</v>
+        <v>1928</v>
       </c>
       <c r="B273" t="n">
-        <v>3582.76869090992</v>
+        <v>1.000859835452184</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -6034,20 +6034,20 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>1984</v>
+        <v>1929</v>
       </c>
       <c r="B274" t="n">
-        <v>3618.4</v>
+        <v>1.00105011791057</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -6057,16 +6057,16 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>1984</v>
+        <v>1930</v>
       </c>
       <c r="B275" t="n">
-        <v>0.990152744558346</v>
+        <v>1.002005181190812</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -6080,20 +6080,20 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>1985</v>
+        <v>1931</v>
       </c>
       <c r="B276" t="n">
-        <v>3784.444548311834</v>
+        <v>1.00158936137145</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -6103,20 +6103,20 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>1985</v>
+        <v>1932</v>
       </c>
       <c r="B277" t="n">
-        <v>3819.3</v>
+        <v>1.001392769842181</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -6126,16 +6126,16 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>1985</v>
+        <v>1933</v>
       </c>
       <c r="B278" t="n">
-        <v>0.9908738638786776</v>
+        <v>1.00213922000205</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -6149,20 +6149,20 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1986</v>
+        <v>1934</v>
       </c>
       <c r="B279" t="n">
-        <v>3955.988767242127</v>
+        <v>1.001537326250401</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -6172,20 +6172,20 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1986</v>
+        <v>1935</v>
       </c>
       <c r="B280" t="n">
-        <v>3989.7</v>
+        <v>1.002248278676314</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -6195,16 +6195,16 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>1986</v>
+        <v>1936</v>
       </c>
       <c r="B281" t="n">
-        <v>0.9915504341785416</v>
+        <v>1.001175093137489</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -6218,20 +6218,20 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>1987</v>
+        <v>1937</v>
       </c>
       <c r="B282" t="n">
-        <v>4163.96217867707</v>
+        <v>1.00106867281749</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -6241,20 +6241,20 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>1987</v>
+        <v>1938</v>
       </c>
       <c r="B283" t="n">
-        <v>4197.6</v>
+        <v>1.000924158443574</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -6264,16 +6264,16 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1987</v>
+        <v>1939</v>
       </c>
       <c r="B284" t="n">
-        <v>0.9919864157321016</v>
+        <v>0.9998938744153005</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -6287,20 +6287,20 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>1988</v>
+        <v>1940</v>
       </c>
       <c r="B285" t="n">
-        <v>4428.610001509143</v>
+        <v>1.000270920465122</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -6310,20 +6310,20 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1988</v>
+        <v>1941</v>
       </c>
       <c r="B286" t="n">
-        <v>4462.9</v>
+        <v>0.999968001687791</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -6333,16 +6333,16 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1988</v>
+        <v>1942</v>
       </c>
       <c r="B287" t="n">
-        <v>0.992316655427893</v>
+        <v>0.999644859672609</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -6356,20 +6356,20 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>1989</v>
+        <v>1943</v>
       </c>
       <c r="B288" t="n">
-        <v>4696.527407332671</v>
+        <v>1.000413401093563</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -6379,20 +6379,20 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>1989</v>
+        <v>1944</v>
       </c>
       <c r="B289" t="n">
-        <v>4728.2</v>
+        <v>1.00017906167382</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -6402,16 +6402,16 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>1989</v>
+        <v>1945</v>
       </c>
       <c r="B290" t="n">
-        <v>0.993301342441663</v>
+        <v>0.9999976205451548</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -6425,20 +6425,20 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>1990</v>
+        <v>1946</v>
       </c>
       <c r="B291" t="n">
-        <v>4961.119421061194</v>
+        <v>0.9962785039910634</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -6448,20 +6448,20 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>1990</v>
+        <v>1947</v>
       </c>
       <c r="B292" t="n">
-        <v>4993.1</v>
+        <v>0.9944300961747021</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -6471,16 +6471,16 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>1990</v>
+        <v>1948</v>
       </c>
       <c r="B293" t="n">
-        <v>0.993595045374856</v>
+        <v>0.9941071901382825</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -6494,20 +6494,20 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>1991</v>
+        <v>1949</v>
       </c>
       <c r="B294" t="n">
-        <v>5075.528851661904</v>
+        <v>0.9946936009664952</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -6517,20 +6517,20 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>1991</v>
+        <v>1950</v>
       </c>
       <c r="B295" t="n">
-        <v>5105.1</v>
+        <v>0.9933683484986656</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -6540,16 +6540,16 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>1991</v>
+        <v>1951</v>
       </c>
       <c r="B296" t="n">
-        <v>0.9942075280918892</v>
+        <v>0.9938759259463967</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -6563,20 +6563,20 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>1992</v>
+        <v>1952</v>
       </c>
       <c r="B297" t="n">
-        <v>5250.82411907481</v>
+        <v>0.9938297772931333</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -6586,20 +6586,20 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>1992</v>
+        <v>1953</v>
       </c>
       <c r="B298" t="n">
-        <v>5275.6</v>
+        <v>0.9941143551806563</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -6609,16 +6609,16 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>1992</v>
+        <v>1954</v>
       </c>
       <c r="B299" t="n">
-        <v>0.995303684713551</v>
+        <v>0.9945897116947772</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -6632,20 +6632,20 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>1993</v>
+        <v>1955</v>
       </c>
       <c r="B300" t="n">
-        <v>5500.592856221755</v>
+        <v>0.9936543011532273</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -6655,20 +6655,20 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>1993</v>
+        <v>1956</v>
       </c>
       <c r="B301" t="n">
-        <v>5523.9</v>
+        <v>0.9931316369088241</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -6678,16 +6678,16 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>1993</v>
+        <v>1957</v>
       </c>
       <c r="B302" t="n">
-        <v>0.995780672391201</v>
+        <v>0.9932381971000073</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -6701,20 +6701,20 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>1994</v>
+        <v>1958</v>
       </c>
       <c r="B303" t="n">
-        <v>5805.960443253049</v>
+        <v>0.9936468607427142</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -6724,20 +6724,20 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>1994</v>
+        <v>1959</v>
       </c>
       <c r="B304" t="n">
-        <v>5823.9</v>
+        <v>0.9940255108919498</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -6747,16 +6747,16 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>1994</v>
+        <v>1960</v>
       </c>
       <c r="B305" t="n">
-        <v>0.9969196660748036</v>
+        <v>0.9942540346388405</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -6770,20 +6770,20 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>1995</v>
+        <v>1961</v>
       </c>
       <c r="B306" t="n">
-        <v>6136.599105605455</v>
+        <v>0.9945841615285803</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -6793,20 +6793,20 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>1995</v>
+        <v>1962</v>
       </c>
       <c r="B307" t="n">
-        <v>6154.2</v>
+        <v>0.9948606966854651</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -6816,16 +6816,16 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>1995</v>
+        <v>1963</v>
       </c>
       <c r="B308" t="n">
-        <v>0.9971400191097876</v>
+        <v>0.9959791082458187</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -6839,20 +6839,20 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>1996</v>
+        <v>1964</v>
       </c>
       <c r="B309" t="n">
-        <v>6451.600519091945</v>
+        <v>0.9967430357595458</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -6862,20 +6862,20 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>1996</v>
+        <v>1965</v>
       </c>
       <c r="B310" t="n">
-        <v>6469.9</v>
+        <v>0.9971174548124043</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -6885,16 +6885,16 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>1996</v>
+        <v>1966</v>
       </c>
       <c r="B311" t="n">
-        <v>0.9971715975659508</v>
+        <v>0.9963382597400294</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -6908,20 +6908,20 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>1997</v>
+        <v>1967</v>
       </c>
       <c r="B312" t="n">
-        <v>6812.173917136629</v>
+        <v>0.9957940612804325</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -6931,20 +6931,20 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>1997</v>
+        <v>1968</v>
       </c>
       <c r="B313" t="n">
-        <v>6830.5</v>
+        <v>0.9949524254210041</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -6954,16 +6954,16 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>1997</v>
+        <v>1969</v>
       </c>
       <c r="B314" t="n">
-        <v>0.9973170217607246</v>
+        <v>0.9941762491752056</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -6977,20 +6977,20 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>1998</v>
+        <v>1970</v>
       </c>
       <c r="B315" t="n">
-        <v>7197.345587275926</v>
+        <v>0.993738673904997</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7000,20 +7000,20 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>1998</v>
+        <v>1971</v>
       </c>
       <c r="B316" t="n">
-        <v>7217.6</v>
+        <v>0.9934677646825514</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -7023,16 +7023,16 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>1998</v>
+        <v>1972</v>
       </c>
       <c r="B317" t="n">
-        <v>0.9971937468515748</v>
+        <v>0.9938002526573482</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -7046,20 +7046,20 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>1999</v>
+        <v>1973</v>
       </c>
       <c r="B318" t="n">
-        <v>7621.627746178</v>
+        <v>0.9929719148904681</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -7069,20 +7069,20 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>1999</v>
+        <v>1974</v>
       </c>
       <c r="B319" t="n">
-        <v>7641.6</v>
+        <v>0.9900318892944598</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -7092,16 +7092,16 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>1999</v>
+        <v>1975</v>
       </c>
       <c r="B320" t="n">
-        <v>0.9973863780069618</v>
+        <v>0.9900390553415785</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -7115,20 +7115,20 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>2000</v>
+        <v>1976</v>
       </c>
       <c r="B321" t="n">
-        <v>8154.627120417485</v>
+        <v>0.9900201357500704</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -7138,20 +7138,20 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>2000</v>
+        <v>1977</v>
       </c>
       <c r="B322" t="n">
-        <v>8175.4</v>
+        <v>0.9900076622312982</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -7161,16 +7161,16 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>2000</v>
+        <v>1978</v>
       </c>
       <c r="B323" t="n">
-        <v>0.9974590993000324</v>
+        <v>0.9891860524133774</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -7184,20 +7184,20 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>2001</v>
+        <v>1979</v>
       </c>
       <c r="B324" t="n">
-        <v>8588.950335181662</v>
+        <v>0.9885883372313006</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -7207,20 +7207,20 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>2001</v>
+        <v>1980</v>
       </c>
       <c r="B325" t="n">
-        <v>8595.6</v>
+        <v>0.9876538794822001</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -7230,16 +7230,16 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>2001</v>
+        <v>1981</v>
       </c>
       <c r="B326" t="n">
-        <v>0.9992263873588419</v>
+        <v>0.9873066826276905</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -7253,20 +7253,20 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>2002</v>
+        <v>1982</v>
       </c>
       <c r="B327" t="n">
-        <v>8900.840268850468</v>
+        <v>0.9885377563597302</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -7276,20 +7276,20 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>2002</v>
+        <v>1983</v>
       </c>
       <c r="B328" t="n">
-        <v>8907.700000000001</v>
+        <v>0.9895256747232776</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -7299,16 +7299,16 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>2002</v>
+        <v>1984</v>
       </c>
       <c r="B329" t="n">
-        <v>0.9992299099487486</v>
+        <v>0.990152744558346</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -7322,20 +7322,20 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>2003</v>
+        <v>1985</v>
       </c>
       <c r="B330" t="n">
-        <v>9178.639804728598</v>
+        <v>0.9908738638786777</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -7345,20 +7345,20 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>2003</v>
+        <v>1986</v>
       </c>
       <c r="B331" t="n">
-        <v>9185.799999999999</v>
+        <v>0.9915504341785416</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -7368,16 +7368,16 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>2003</v>
+        <v>1987</v>
       </c>
       <c r="B332" t="n">
-        <v>0.9992205147868012</v>
+        <v>0.9919864157321017</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -7391,20 +7391,20 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>2004</v>
+        <v>1988</v>
       </c>
       <c r="B333" t="n">
-        <v>9904.847948333394</v>
+        <v>0.992316655427893</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -7414,20 +7414,20 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>2004</v>
+        <v>1989</v>
       </c>
       <c r="B334" t="n">
-        <v>9909.5</v>
+        <v>0.993301342441663</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -7437,16 +7437,16 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>2004</v>
+        <v>1990</v>
       </c>
       <c r="B335" t="n">
-        <v>0.9995305462771475</v>
+        <v>0.993595045374856</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -7460,20 +7460,20 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>2005</v>
+        <v>1991</v>
       </c>
       <c r="B336" t="n">
-        <v>10780.81498817506</v>
+        <v>0.9942075280918892</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -7483,20 +7483,20 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>2005</v>
+        <v>1992</v>
       </c>
       <c r="B337" t="n">
-        <v>10768.3</v>
+        <v>0.995303684713551</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -7506,16 +7506,16 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>2005</v>
+        <v>1993</v>
       </c>
       <c r="B338" t="n">
-        <v>1.001162206492674</v>
+        <v>0.995780672391201</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -7529,20 +7529,20 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>2006</v>
+        <v>1994</v>
       </c>
       <c r="B339" t="n">
-        <v>11684.02682902413</v>
+        <v>0.9969196660748036</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -7552,20 +7552,20 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>2006</v>
+        <v>1995</v>
       </c>
       <c r="B340" t="n">
-        <v>11679.9</v>
+        <v>0.9971400191097877</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -7575,16 +7575,16 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>2006</v>
+        <v>1996</v>
       </c>
       <c r="B341" t="n">
-        <v>1.000353327427814</v>
+        <v>0.9971715975659509</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -7598,20 +7598,20 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>2007</v>
+        <v>1997</v>
       </c>
       <c r="B342" t="n">
-        <v>12317.43528738132</v>
+        <v>0.9973170217607246</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -7621,20 +7621,20 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>2007</v>
+        <v>1998</v>
       </c>
       <c r="B343" t="n">
-        <v>12317.8</v>
+        <v>0.9971937468515747</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -7644,16 +7644,16 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>2007</v>
+        <v>1999</v>
       </c>
       <c r="B344" t="n">
-        <v>0.9999703914157824</v>
+        <v>0.9973863780069618</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -7667,20 +7667,20 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="B345" t="n">
-        <v>13141.3387796931</v>
+        <v>0.9974590993000325</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -7690,20 +7690,20 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="B346" t="n">
-        <v>13138</v>
+        <v>0.9992263873588419</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -7713,16 +7713,16 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="B347" t="n">
-        <v>1.000254131503509</v>
+        <v>0.9992299099487486</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -7736,20 +7736,20 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="B348" t="n">
-        <v>12704.12906671262</v>
+        <v>0.9992205147868013</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -7759,20 +7759,20 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="B349" t="n">
-        <v>12701.7</v>
+        <v>0.9995305462771475</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -7782,16 +7782,16 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="B350" t="n">
-        <v>1.000191239496494</v>
+        <v>1.001162206492674</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -7805,20 +7805,20 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="B351" t="n">
-        <v>12996.26449013909</v>
+        <v>1.000353327427814</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -7828,20 +7828,20 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="B352" t="n">
-        <v>12994.6</v>
+        <v>0.9999703914157825</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -7851,16 +7851,16 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B353" t="n">
-        <v>1.00012809091</v>
+        <v>1.000254131503509</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -7874,20 +7874,20 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B354" t="n">
-        <v>13531.21957541143</v>
+        <v>1.000191239496494</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>XS005-A</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -7897,20 +7897,20 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B355" t="n">
-        <v>13530.8</v>
+        <v>1.000128090910001</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>XS005-B</t>
+          <t>XS005-C</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>billions_current_usd</t>
+          <t>dimensionless_ratio</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pure reference regenerator; verifies 99.6% accuracy of the GPIM rule (Appendix Table 6.8.II.1). Sensitivity variant — NOT used by S601-S604. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
+          <t>Pure reference regenerator; verifies 99.6% accuracy of the Generalized Perpetual Inventory Method (GPIM) rule (Appendix Table 6.8.II.1). Sensitivity variant — NOT used by S601-S604.</t>
         </is>
       </c>
     </row>
@@ -8093,7 +8093,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
+          <t>The canonical Shaikh-published values are transcribed from the published Chapter 6 appendix workbook (Shaikh 2016, Appendix 6.8). Upstream agencies are the Bureau of Economic Analysis (BEA) — its National Income and Product Accounts (NIPA) and Fixed Asset accounts (FA) — the IRS Statistics of Income (SOI), the U.S. Census Bureau (Historical Statistics 1975, for IRS book values), and the Federal Reserve Board G.17 industrial-production release (FRB G.17). All public domain.</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>`V03_XS005_validate.py` round-trip-validates against the Appendix 6.8 source workbook at 1.0% tolerance. Per the Phase 4 adequacy report (`CH6_ADEQUACY_REPORT.json`), Phase 5 blockers B2 (NIPA T7.11 FISIM remap, resolver in `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
+          <t>The validation step round-trips the constructed series against the Appendix 6.8 source workbook at a 1.0% tolerance. Two data-sourcing steps needed for this construction are resolved: the remap of financial services indirectly measured (FISIM) in NIPA Table 7.11, and the 1993 BEA depreciation rates.</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published XS005 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
+          <t>Under the Chapter 6 Generalized Perpetual Inventory Method (GPIM) construction pipeline, and following the principle that extended values must be rebuilt from sources rather than spliced, **extension does NOT splice the published XS005 values**. Instead, the extension re-fetches the underlying National Income and Product Accounts (NIPA), BEA Fixed Asset, IRS, and Census components and re-runs the formula end-to-end at the current vintage.</t>
         </is>
       </c>
     </row>
@@ -8266,14 +8266,14 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
+          <t>1. Fetch the BEA NIPA tables via the BEA data API (a BEA API key is required), using the table ids documented for this series' primary source.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
+          <t>2. Fetch BEA Fixed Asset Tables 6.1, 6.4, 6.7, 6.8 from the same source.</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>For XS005, the Phase 5 round-trip validation reads `XS005_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1925-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
+          <t>For XS005, the round-trip validation reads the raw series from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1925-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>## No-Proxy Disclosure</t>
+          <t>## Source substitutions</t>
         </is>
       </c>
     </row>
@@ -8333,7 +8333,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>## No-Synthetic Disclosure</t>
+          <t>## Forecast vs. observed data</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
+          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified against the staged 1993 BEA depreciation inputs).</t>
         </is>
       </c>
     </row>
@@ -8377,35 +8377,35 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
+          <t>| Appendix workbook missing or corrupted | The appendix loader raises a file-not-found error or returns an empty table | The load step returns a FAIL status naming the missing file |</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
+          <t>| Variable name not in workbook | The variable lookup returns no rows | The load step records 0 rows for that subseries; validation flags it as missing |</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
+          <t>| BEA / IRS vintage drift during extension | The documented re-fetch script logs the vintage year; validation tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>| FISIM T7.11 line revision (XS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
+          <t>| FISIM (financial services indirectly measured) revision to NIPA Table 7.11 line numbers (affects XS003) | The Table 7.11 line resolver falls back to the nearest pinned vintage with a logged warning | Lines are re-mapped by their published stub labels; the vintage used is logged |</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>| BEA 1993 depreciation rate not available post-2011 | XS004/XS006/XS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
+          <t>| BEA 1993 depreciation rate not available post-2011 | The capital-stock series (XS004 and related) freeze depreciation-rate inputs at the 2011-vintage projection | Documented with the staged 1993 BEA methodology inputs |</t>
         </is>
       </c>
     </row>
@@ -8415,7 +8415,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>## CD2 Divergence Pre-Disclosure</t>
+          <t>## Comparison with the earlier replication</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
+          <t>Round-trip parity with an earlier replication is expected within tolerance for the book period. The comparison against that earlier replication's per-series output is informational only, when available.</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8435,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>## Anti-Degradation Compliance</t>
+          <t>## Extension integrity</t>
         </is>
       </c>
     </row>
@@ -8445,7 +8445,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Per Anu Framework: extension MUST re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end. Splicing the published series is FORBIDDEN. Loader caches BEA / FRED responses per `S00_cache` with 30-day TTL (book-period values: TTL=None).</t>
+          <t>Extension MUST re-fetch the BEA, IRS, and Federal Reserve Board (FRB) component series and re-compute the formula end-to-end; splicing the published series is forbidden. The loader caches BEA and FRED responses for 30 days (book-period values are cached permanently).</t>
         </is>
       </c>
     </row>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T22:48:59.058054+00:00</t>
+          <t>2026-07-02T06:26:59.774506+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS005_extenbook.xlsx
+++ b/extenbooks/XS005_extenbook.xlsx
@@ -8804,7 +8804,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:26:59.774506+00:00</t>
+          <t>2026-07-11T03:44:27.472509+00:00</t>
         </is>
       </c>
     </row>
@@ -8819,11 +8819,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8846,6 +8846,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_6_8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Methodology variant of XS004 (NOT used by S601-S604) that re-derives the official BEA 2011 net stock from the pure GPIM rule, verifying ~99.6% accuracy of the accumulation rule (Appendix Table 6.8.II.1). Publishes because it documents the GPIM-rule validation Shaikh relies on and renders sensibly once units are split: XS005-C is the GPIM/BEA ratio (~1.0), which must not share the billions axis with the two stock columns (latent mixed-units, fixed here per UNITS_VALIDATION_STANDARD).", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS005_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS005_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pure reference regenerator; verifies 99.6% accuracy of the GPIM rule (Appendix Table 6.8.II.1). Sensitivity variant — NOT used by S601-S604.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>per_subseries</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
